--- a/data/trans_orig/IP07KS_C05_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C05_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1147</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>3</t>
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36117</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>25697</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>43526</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>66,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>47,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>21201</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>6192</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>40175</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>37901</t>
+          <t>22230</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27035</t>
+          <t>15345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45934</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59103</t>
+          <t>58346</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27513</t>
+          <t>47082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81193</t>
+          <t>68712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>73,99%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>13543</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6914</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25427</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>37034</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15051</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>54971</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>59,87%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>24,33%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28441</t>
+          <t>18782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>52074</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87197</t>
+          <t>37901</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>40,81%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2839</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7593</t>
+          <t>10330</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>7178</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -1741,107 +1741,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3535</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4154</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -1854,107 +1854,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>946</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4253</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5088</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>5771</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5463</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>54391</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>61857</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57860</t>
+          <t>38481</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>119717</t>
+          <t>92871</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12863</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9043</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16671</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>55,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>39,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9585</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5751</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>13108</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>45,93%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>27,56%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>62,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>9455</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18331</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>23770</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29546</t>
+          <t>27413</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>62,41%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4688</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2310</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8737</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>6574</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>10116</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>31,5%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,47%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9439</t>
+          <t>10412</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16482</t>
+          <t>16292</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2642</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>660</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5847</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,45%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>25,34%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>3530</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6840</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>32,78%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11725</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>26,69%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2438,12 +2438,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -2536,107 +2536,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5305</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>7,02%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6325</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>24,88%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1877</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6438</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>23078</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20869</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>20850</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46287</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,74 +2766,74 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>14806</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8260</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>47,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2486</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>93,85%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2556</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2938</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>87,01%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>24,07%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>17085</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>9847</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>19750</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>86,51%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>49,86%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
           <t>9</t>
@@ -2841,27 +2841,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>11845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2879,107 +2879,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1895</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2231</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>12,99%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>71,53%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>75,93%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>2521</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1569</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -3105,107 +3105,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1526</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>44,2%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>8421</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1526</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>7040</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>7,49%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>42,64%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1516</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>7973</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>34,56%</t>
         </is>
       </c>
     </row>
@@ -3218,107 +3218,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>5890</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1149</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>6631</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1099</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>6318</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>5,4%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>33,57%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1149</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>6040</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>17431</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>19750</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>20369</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>9578</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>6427</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13085</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>47,22%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>64,51%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>10201</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>7142</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>12366</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>69,4%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>48,59%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>84,13%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5853</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12562</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>20314</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>15151</t>
+          <t>15476</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>24020</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,18%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9482</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>5950</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>12882</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>46,74%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>29,33%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>63,51%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>1857</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>7062</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>27,85%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>48,04%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9427</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6234</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>7491</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>48,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>13521</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9823</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>18568</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -3674,107 +3674,107 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2321</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2781</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>17,86%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>541</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -3787,107 +3787,107 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>595</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2,93%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>14,77%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>3028</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>630</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>3203</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2549</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>622</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>2560</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>20285</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14698</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6019</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2937</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>9545</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>30,94%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>49,07%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>7167</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>9,64%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>40,59%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3351</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>10375</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>14671</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,58%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10335</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6849</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>14126</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>53,13%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>35,21%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>72,62%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>12059</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>8753</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>14505</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>49,56%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15591</t>
+          <t>15597</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>23619</t>
+          <t>23000</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>28366</t>
+          <t>27775</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>2517</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>5902</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12,94%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>1053</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3523</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>19,04%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>2445</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>6127</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1167</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7382</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -4469,107 +4469,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>580</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>3172</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
+      <c r="P37" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J37" s="2" t="inlineStr">
+      <c r="Q37" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>2492</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>11,9%</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T37" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
-        </is>
-      </c>
-      <c r="U37" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="V37" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -4582,107 +4582,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>3291</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2874</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>3,08%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>572</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="inlineStr">
-        <is>
-          <t>543</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T38" s="2" t="inlineStr">
-        <is>
-          <t>2653</t>
-        </is>
-      </c>
-      <c r="U38" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V38" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38024</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38024</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38024</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>27226</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>20730</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>34241</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>57,25%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>43,59%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>72,0%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10029</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>6124</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>14445</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>22,44%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>52,92%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>10495</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>20127</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>36434</t>
+          <t>37721</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28797</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>44952</t>
+          <t>46059</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>12123</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>18954</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>25,49%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>15,21%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>7437</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>3799</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>12346</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>27,25%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>7829</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>18014</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>19184</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13044</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>25759</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>37,09%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>5589</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>10542</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>11,75%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>22,17%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>9138</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>5593</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>13817</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>33,48%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>20,49%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>50,62%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>5417</t>
+          <t>9747</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>10729</t>
+          <t>14898</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>51,65%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>14555</t>
+          <t>15336</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>23090</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -5151,107 +5151,107 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>863</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>4414</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>9,28%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I43" s="2" t="inlineStr">
+      <c r="P43" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J43" s="2" t="inlineStr">
+      <c r="Q43" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>4693</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>4568</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>1758</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>11,77%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>692</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>3755</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>1721</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>5710</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>767</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>6931</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>47558</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>27295</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>46141</t>
+          <t>28843</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>73436</t>
+          <t>76401</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5494,72 +5494,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11257</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6382</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>18198</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>12,9%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>20,86%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>7162</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>3827</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>13139</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>11,28%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>20,69%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>7654</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>3986</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5569,32 +5569,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>17428</t>
+          <t>18912</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>25462</t>
+          <t>28035</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -5607,72 +5607,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>58746</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>49505</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>66604</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>67,33%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>56,74%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>76,34%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>41871</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>35391</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>48173</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>65,93%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>55,73%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>75,86%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>54389</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>45862</t>
+          <t>38853</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>61839</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5682,32 +5682,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>96260</t>
+          <t>105069</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>84867</t>
+          <t>93364</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>106701</t>
+          <t>115988</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>59,23%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -5720,72 +5720,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>3743</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>14503</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>9,02%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>9280</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>4984</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>15294</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>18120</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5795,32 +5795,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>16427</t>
+          <t>18916</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>11770</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>24932</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -5833,72 +5833,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>4203</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>8719</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>9,99%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>5191</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>2295</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>10787</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>1487</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>11247</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5908,32 +5908,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4937</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>15285</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -5946,107 +5946,107 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
+          <t>1897</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>11493</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>5,93%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>13,17%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I50" s="2" t="inlineStr">
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J50" s="2" t="inlineStr">
+      <c r="Q50" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>1871</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr">
-        <is>
-          <t>12160</t>
-        </is>
-      </c>
-      <c r="N50" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="O50" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="P50" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -6059,57 +6059,57 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>87249</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>63504</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>81315</t>
+          <t>70393</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6134,17 +6134,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>144819</t>
+          <t>157642</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6176,72 +6176,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>117866</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>101462</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>137781</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>64668</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>40955</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>79839</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>121557</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6251,32 +6251,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>186225</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>164115</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>209276</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -6289,72 +6289,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>109573</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>93460</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>125611</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>110406</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>91211</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>144134</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>89311</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>126741</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6364,32 +6364,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>218472</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>261467</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -6402,72 +6402,72 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>22403</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>14945</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>17308</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6477,32 +6477,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -6515,72 +6515,72 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>7154</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>13524</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6590,32 +6590,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -6628,72 +6628,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>19476</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>20713</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6703,32 +6703,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -6741,57 +6741,57 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>272147</t>
+          <t>196798</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
